--- a/working/s6_026-UNET_ILP_095_eda_features_metrics.xlsx
+++ b/working/s6_026-UNET_ILP_095_eda_features_metrics.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,25 +430,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>特徴量名 (和名)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>系統階層</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>簡単な一行説明</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>算出式</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROC-AUC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>分離方向</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cohen's d</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>最大F1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>最適足切り閾値</t>
         </is>
@@ -465,21 +485,39 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>GT最近傍距離 (μm)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>推論ノードと最も近いGT細胞ノードとの3D空間物理距離</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>min(||p_pred - p_gt|| * scale)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
+        <v>-1.0484</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>24.04</v>
       </c>
     </row>
@@ -494,21 +532,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>ステップ速度変動係数</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>トラック内のフレーム間移動速度のばらつき比率 (等速性の指標)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>std(step_velocities) / (mean(step_velocities) + 1e-5)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0.8752</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.2206</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.0253</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>0.7386</v>
       </c>
     </row>
@@ -523,21 +579,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>XY画像中心距離 (μm)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>視野中心からのXY平面上の物理距離 (中心集中傾向の指標)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sqrt(((y - Y/2)*sy)^2 + ((x - X/2)*sx)^2)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0.8554</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
+        <v>-1.3863</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.0331</v>
       </c>
-      <c r="G4" t="n">
+      <c r="K4" t="n">
         <v>11.83</v>
       </c>
     </row>
@@ -552,21 +626,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>XY境界最近接距離 (μm)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>XY画像境界(端点)までの最短物理距離 (端の途切れ検知)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>min(y, Y-1-y, x, X-1-x) * s_xy</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0.8526</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.0316</v>
       </c>
-      <c r="G5" t="n">
+      <c r="K5" t="n">
         <v>41.84</v>
       </c>
     </row>
@@ -581,21 +673,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>3x3局所最小輝度</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ノード中心周辺3x3x3ボクセルの最小画素輝度値</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>min(I[z-1:z+2, y-1:y+2, x-1:x+2])</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0.7887</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9248</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.0126</v>
       </c>
-      <c r="G6" t="n">
+      <c r="K6" t="n">
         <v>1350</v>
       </c>
     </row>
@@ -610,21 +720,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>3x3局所平均輝度</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ノード中心周辺3x3x3ボクセルの平均画素輝度値</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mean(I[z-1:z+2, y-1:y+2, x-1:x+2])</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0.7677</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8453000000000001</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.0125</v>
       </c>
-      <c r="G7" t="n">
+      <c r="K7" t="n">
         <v>1567.602</v>
       </c>
     </row>
@@ -639,21 +767,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>生画素輝度</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>検出ノード中心ボクセルの生輝度値 (細胞核の中心輝度)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>I[z, y, x]</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>0.7647</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.0125</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
         <v>1685</v>
       </c>
     </row>
@@ -668,21 +814,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>トラック平均輝度</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>トラックを構成する全細胞ノードの平均画素輝度</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>mean_{v in track}(raw_intensity)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>0.7631</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7947</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.0074</v>
       </c>
-      <c r="G9" t="n">
+      <c r="K9" t="n">
         <v>1292.2085</v>
       </c>
     </row>
@@ -697,21 +861,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>3x3局所最大輝度</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ノード中心周辺3x3x3ボクセルの最大画素輝度値</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>max(I[z-1:z+2, y-1:y+2, x-1:x+2])</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>0.7487</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.7704</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.0118</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>1717</v>
       </c>
     </row>
@@ -726,21 +908,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>軌跡直進性比率</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>正味直線変位と総移動経路長の比率 (1.0に近いほど直進)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>net_displacement / total_path_length</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>0.7359</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7707000000000001</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
         <v>0.7089</v>
       </c>
     </row>
@@ -755,21 +955,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>空間拘束比</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>正味直線変位と総移動経路長の比率 (遊走か停滞かの指標)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>net_displacement / total_path_length</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>0.7337</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7601</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G12" t="n">
+      <c r="K12" t="n">
         <v>0.711</v>
       </c>
     </row>
@@ -784,21 +1002,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>トラック最大輝度</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>トラック内の細胞ノードが記録した最大輝度値</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>max_{v in track}(raw_intensity)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>0.7137</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G13" t="n">
+      <c r="K13" t="n">
         <v>1938</v>
       </c>
     </row>
@@ -813,21 +1049,39 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>最寄りノード距離 (μm)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>同一フレーム内で最も近い他ノードまでの3D空間距離</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>min_{j != i} ||p_i - p_j|| * scale</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>0.7103</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
+        <v>-0.5842000000000001</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.0092</v>
       </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
         <v>7.96</v>
       </c>
     </row>
@@ -842,21 +1096,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>トラック輝度標準偏差</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>トラック内の細胞ノード輝度の時間的変動幅</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>std_{v in track}(raw_intensity)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>0.7101</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.0086</v>
       </c>
-      <c r="G15" t="n">
+      <c r="K15" t="n">
         <v>266.7855</v>
       </c>
     </row>
@@ -871,21 +1143,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>10μm近傍ノード数</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>半径10μm球体内に存在する他ノードの個数 (局所細胞密度)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>|{j | ||p_i - p_j|| * scale &lt;= 10μm}| - 1</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>0.6892</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6365</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="G16" t="n">
+      <c r="K16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -900,21 +1190,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>正味直線変位 (μm)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>トラック始点から終点までの3D直線物理距離</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>||p_end - p_start|| * scale</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>0.6773</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8839</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.0253</v>
       </c>
-      <c r="G17" t="n">
+      <c r="K17" t="n">
         <v>113.8605</v>
       </c>
     </row>
@@ -929,21 +1237,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>方向性遊走指標</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>直進性と平均速度を掛け合わせた複合遊走指標</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>straightness_ratio * mean_velocity</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>0.6722</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.0253</v>
       </c>
-      <c r="G18" t="n">
+      <c r="K18" t="n">
         <v>12.0968</v>
       </c>
     </row>
@@ -958,21 +1284,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>局所コントラスト</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>局所パッチ内の明暗差と平均輝度の比 (細胞輪郭コントラスト)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(int_max - int_min) / (int_mean + 1e-5)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>0.6707</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
+        <v>-0.5152</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="G19" t="n">
+      <c r="K19" t="n">
         <v>0.2054</v>
       </c>
     </row>
@@ -987,21 +1331,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>存続フレーム数</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>トラックが観測され続けた時間長 (フレーム数)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>t_end - t_start</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>0.6624</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6095</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.0124</v>
       </c>
-      <c r="G20" t="n">
+      <c r="K20" t="n">
         <v>49</v>
       </c>
     </row>
@@ -1016,21 +1378,39 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>トラックノード数</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>トラックに含まれる細胞ノードの総数</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>len(nodes in track)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>0.6618000000000001</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6022</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.0124</v>
       </c>
-      <c r="G21" t="n">
+      <c r="K21" t="n">
         <v>49</v>
       </c>
     </row>
@@ -1045,21 +1425,39 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>15μm近傍ノード数</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>半径15μm球体内に存在する他ノードの個数</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>|{j | ||p_i - p_j|| * scale &lt;= 15μm}| - 1</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>0.6595</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5173</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.0077</v>
       </c>
-      <c r="G22" t="n">
+      <c r="K22" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1074,21 +1472,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>総移動経路長 (μm)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>トラックの各ステップの3D移動距離の総和</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>sum(||p_{t+1} - p_t|| * scale)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>0.6461</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.0128</v>
       </c>
-      <c r="G23" t="n">
+      <c r="K23" t="n">
         <v>137.502</v>
       </c>
     </row>
@@ -1103,21 +1519,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>ラプラシアン鮮鋭度</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>画素中心と局所両極値との二次微分的差異 (輪郭の鮮鋭さ)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>|2 * raw_int - int_min - int_max|</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>0.6293</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="J24" t="n">
         <v>0.0075</v>
       </c>
-      <c r="G24" t="n">
+      <c r="K24" t="n">
         <v>292</v>
       </c>
     </row>
@@ -1132,21 +1566,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>最大ステップ長 (μm)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>トラック内で記録された1フレーム間の最大移動距離</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>max(step_distances)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>0.6264999999999999</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="J25" t="n">
         <v>0.0074</v>
       </c>
-      <c r="G25" t="n">
+      <c r="K25" t="n">
         <v>7.27</v>
       </c>
     </row>
@@ -1161,21 +1613,39 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>SNR変化量</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>接続元ノードと接続先ノードの局所SNRの絶対差</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>|snr_src - snr_tgt|</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>0.618</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="I26" t="n">
+        <v>-0.4044</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G26" t="n">
+      <c r="K26" t="n">
         <v>0.4402</v>
       </c>
     </row>
@@ -1190,21 +1660,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>軌跡主軸アスペクト比</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3D軌跡の主成分分析(PCA)主軸比 (直進か等方分散かの判定)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>lambda_1 / (lambda_2 + 1e-5)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>0.6176</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.1188</v>
+      </c>
+      <c r="J27" t="n">
         <v>0.0052</v>
       </c>
-      <c r="G27" t="n">
+      <c r="K27" t="n">
         <v>19.2809</v>
       </c>
     </row>
@@ -1219,21 +1707,39 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Z軸変位 (μm)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>接続元から接続先へのZ方向の符号付き物理移動量</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(z_tgt - z_src) * s_z</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>0.6082</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="J28" t="n">
         <v>0.0067</v>
       </c>
-      <c r="G28" t="n">
+      <c r="K28" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -1248,21 +1754,39 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>トラック最大SNR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>トラック内の細胞ノードが記録した最大局所SNR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>max_{v in track}(local_snr)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>0.599</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="I29" t="n">
+        <v>-0.1557</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.0052</v>
       </c>
-      <c r="G29" t="n">
+      <c r="K29" t="n">
         <v>2.7504</v>
       </c>
     </row>
@@ -1277,21 +1801,39 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>3x3局所輝度標準偏差</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>局所パッチ内の輝度ばらつき (テクスチャ複雑度)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>std(I[z-1:z+2, y-1:y+2, x-1:x+2])</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>0.5946</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.006</v>
       </c>
-      <c r="G30" t="n">
+      <c r="K30" t="n">
         <v>118.98</v>
       </c>
     </row>
@@ -1306,21 +1848,39 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>正味前進速度 (μm/frame)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>正味変位を存続フレーム数で割った平均前進速度</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>total_disp_um / max(1, duration_frames)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
         <v>0.5944</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="J31" t="n">
         <v>0.0051</v>
       </c>
-      <c r="G31" t="n">
+      <c r="K31" t="n">
         <v>2.07</v>
       </c>
     </row>
@@ -1335,21 +1895,39 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>トラック最小輝度</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>トラック内の細胞ノードが記録した最小輝度値</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>min_{v in track}(raw_intensity)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>0.5894</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="J32" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G32" t="n">
+      <c r="K32" t="n">
         <v>1132.2</v>
       </c>
     </row>
@@ -1364,21 +1942,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Z軸移動距離 (μm)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Z軸方向の移動距離の絶対値</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>|dz_um|</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>0.588</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="J33" t="n">
         <v>0.0064</v>
       </c>
-      <c r="G33" t="n">
+      <c r="K33" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -1393,21 +1989,39 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>トラック平均SNR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>トラックを構成する全細胞ノードの平均局所SNR</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>mean_{v in track}(local_snr)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>0.5828</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="I34" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="J34" t="n">
         <v>0.0043</v>
       </c>
-      <c r="G34" t="n">
+      <c r="K34" t="n">
         <v>2.7209</v>
       </c>
     </row>
@@ -1422,21 +2036,39 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Transformer接続確率</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SimpleNodeTransformerが予測した時空間接続確率スコア</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>P(edge)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>0.5809</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="J35" t="n">
         <v>0.0059</v>
       </c>
-      <c r="G35" t="n">
+      <c r="K35" t="n">
         <v>0.9829</v>
       </c>
     </row>
@@ -1451,21 +2083,39 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>3Dユークリッド変位 (μm)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>前後フレーム間の細胞3D移動距離</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>sqrt(dz^2 + dy^2 + dx^2)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
         <v>0.577</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="J36" t="n">
         <v>0.01</v>
       </c>
-      <c r="G36" t="n">
+      <c r="K36" t="n">
         <v>5.39</v>
       </c>
     </row>
@@ -1480,21 +2130,39 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>フレーム間移動速度 (μm/frame)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>単位フレームあたりの物理移動速度</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>dist_3d_um / max(1, dt)</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>0.577</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="J37" t="n">
         <v>0.01</v>
       </c>
-      <c r="G37" t="n">
+      <c r="K37" t="n">
         <v>5.39</v>
       </c>
     </row>
@@ -1509,21 +2177,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>前時刻進行方向コサイン類似度</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>直前の移動ベクトルと現在の移動ベクトルのなす角 (慣性・直進性)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>(v_prev · v_curr) / (||v_prev|| * ||v_curr||)</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>0.5719</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="J38" t="n">
         <v>0.0054</v>
       </c>
-      <c r="G38" t="n">
+      <c r="K38" t="n">
         <v>0.3333</v>
       </c>
     </row>
@@ -1538,21 +2224,39 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>平均ステップ長 (μm)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>トラックの1フレームあたりの平均移動距離</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>path_length_um / (track_length - 1)</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
         <v>0.5618</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2104</v>
+      </c>
+      <c r="J39" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G39" t="n">
+      <c r="K39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1567,21 +2271,39 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>輝度差分</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>接続元ノードと接続先ノードの生輝度の絶対差</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>|raw_int_src - raw_int_tgt|</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
         <v>0.5616</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="I40" t="n">
+        <v>-0.2806</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.0051</v>
       </c>
-      <c r="G40" t="n">
+      <c r="K40" t="n">
         <v>153</v>
       </c>
     </row>
@@ -1596,21 +2318,39 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>次時刻進行方向コサイン類似度</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>現在の移動ベクトルと次ステップ候補ベクトルのなす角</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>(v_curr · v_next) / (||v_curr|| * ||v_next||)</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
         <v>0.5563</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2236</v>
+      </c>
+      <c r="J41" t="n">
         <v>0.0054</v>
       </c>
-      <c r="G41" t="n">
+      <c r="K41" t="n">
         <v>0.9487</v>
       </c>
     </row>
@@ -1625,21 +2365,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>X軸変位 (μm)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>接続元から接続先へのX方向の符号付き物理移動量</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>(x_tgt - x_src) * s_x</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>0.5495</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="J42" t="n">
         <v>0.0074</v>
       </c>
-      <c r="G42" t="n">
+      <c r="K42" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -1654,21 +2412,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>X画素座標</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>画像内のX軸ボクセルインデックス</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>0.5466</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="I43" t="n">
+        <v>-0.1389</v>
+      </c>
+      <c r="J43" t="n">
         <v>0.0058</v>
       </c>
-      <c r="G43" t="n">
+      <c r="K43" t="n">
         <v>136</v>
       </c>
     </row>
@@ -1683,21 +2459,39 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>正規化X座標</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0〜1に正規化されたX軸位置</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>x / (X_max - 1)</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>0.5466</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="I44" t="n">
+        <v>-0.1389</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.0058</v>
       </c>
-      <c r="G44" t="n">
+      <c r="K44" t="n">
         <v>0.5333</v>
       </c>
     </row>
@@ -1712,21 +2506,39 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>XY平面変位 (μm)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>XY平面上での物理移動距離</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>sqrt(dy^2 + dx^2)</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>0.5435</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2097</v>
+      </c>
+      <c r="J45" t="n">
         <v>0.0083</v>
       </c>
-      <c r="G45" t="n">
+      <c r="K45" t="n">
         <v>3.63</v>
       </c>
     </row>
@@ -1741,21 +2553,39 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Zスライス座標</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3次元スタック内のZスライスインデックス</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
         <v>0.5414</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G46" t="n">
+      <c r="K46" t="n">
         <v>61</v>
       </c>
     </row>
@@ -1770,21 +2600,39 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>正規化Z座標</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0〜1に正規化されたZ軸深さ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>z / (Z_max - 1)</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>0.5414</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="J47" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G47" t="n">
+      <c r="K47" t="n">
         <v>0.9683</v>
       </c>
     </row>
@@ -1799,21 +2647,39 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Y画素座標</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>画像内のY軸ボクセルインデックス</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
         <v>0.5328000000000001</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
+        <v>-0.0839</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="G48" t="n">
+      <c r="K48" t="n">
         <v>132</v>
       </c>
     </row>
@@ -1828,21 +2694,39 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>正規化Y座標</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0〜1に正規化されたY軸位置</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>y / (Y_max - 1)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>0.5328000000000001</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="I49" t="n">
+        <v>-0.0839</v>
+      </c>
+      <c r="J49" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="G49" t="n">
+      <c r="K49" t="n">
         <v>0.5175999999999999</v>
       </c>
     </row>
@@ -1857,21 +2741,39 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>局所SNR</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>局所パッチ内の輝度コントラストと標準偏差の比</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>(raw_int - int_min) / (int_std + 1e-5)</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>0.5296</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="J50" t="n">
         <v>0.0053</v>
       </c>
-      <c r="G50" t="n">
+      <c r="K50" t="n">
         <v>2.4702</v>
       </c>
     </row>
@@ -1886,21 +2788,39 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>平均推測航法残差 (μm)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>前後ステップ等速直線運動予測位置と実際位置の平均誤差</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>(dead_reck_fwd + dead_reck_bwd) / 2</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>0.5254</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="J51" t="n">
         <v>0.0075</v>
       </c>
-      <c r="G51" t="n">
+      <c r="K51" t="n">
         <v>6.89</v>
       </c>
     </row>
@@ -1915,21 +2835,39 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>前向き推測航法残差 (μm)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>直前ステップの速度ベクトルを外挿した予測位置からのズレ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>||v_curr - v_prev||</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
         <v>0.5183</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="J52" t="n">
         <v>0.0059</v>
       </c>
-      <c r="G52" t="n">
+      <c r="K52" t="n">
         <v>6.89</v>
       </c>
     </row>
@@ -1944,21 +2882,39 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>後向き推測航法残差 (μm)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>次ステップの逆向き速度ベクトルを外挿した予測位置からのズレ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>||v_next - v_curr||</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
         <v>0.5145999999999999</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="J53" t="n">
         <v>0.007</v>
       </c>
-      <c r="G53" t="n">
+      <c r="K53" t="n">
         <v>6.7</v>
       </c>
     </row>
@@ -1973,21 +2929,39 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>トラック最小SNR</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>トラック (Track)</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>トラック内の細胞ノードが記録した最小局所SNR</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>min_{v in track}(local_snr)</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>0.5092</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.0043</v>
       </c>
-      <c r="G54" t="n">
+      <c r="K54" t="n">
         <v>2.1102</v>
       </c>
     </row>
@@ -2002,21 +2976,39 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>5μm近傍ノード数</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>半径5μm球体内に存在する他ノードの個数 (密集・重複検知)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>|{j | ||p_i - p_j|| * scale &lt;= 5μm}| - 1</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
         <v>0.5084</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="I55" t="n">
+        <v>-0.1288</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.0046</v>
       </c>
-      <c r="G55" t="n">
+      <c r="K55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2031,21 +3023,39 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>前向き競合距離マージン (μm)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>第1候補ノードと第2候補ノードの距離差 (曖昧さの指標)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>dist_cand2 - dist_cand1</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>0.5073</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1219</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G56" t="n">
+      <c r="K56" t="n">
         <v>999</v>
       </c>
     </row>
@@ -2060,21 +3070,39 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>15μm競合候補数</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>半径15μm以内に存在する接続先候補ノードの総数</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>|candidates in 15μm|</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>0.5073</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="I57" t="n">
+        <v>-0.1202</v>
+      </c>
+      <c r="J57" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G57" t="n">
+      <c r="K57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2089,21 +3117,39 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>10μm競合候補数</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>半径10μm以内に存在する接続先候補ノードの総数</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>|candidates in 10μm|</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>0.5073</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="I58" t="n">
+        <v>-0.1206</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G58" t="n">
+      <c r="K58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2118,21 +3164,39 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Z境界スライス距離</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Z軸の上下端(第0面または最終面)までのスライス面数</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>min(z, Z_max - 1 - z)</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>0.5071</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="J59" t="n">
         <v>0.0068</v>
       </c>
-      <c r="G59" t="n">
+      <c r="K59" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2147,21 +3211,39 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>輝度比率</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>接続先ノードと接続元ノードの生輝度比</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>raw_int_src / (raw_int_tgt + 1e-5)</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
         <v>0.5061</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.005</v>
       </c>
-      <c r="G60" t="n">
+      <c r="K60" t="n">
         <v>0.9468</v>
       </c>
     </row>
@@ -2176,21 +3258,39 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>SNR比率</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>接続先ノードと接続元ノードの局所SNR比</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>snr_src / (snr_tgt + 1e-5)</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>0.5042</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.0049</v>
       </c>
-      <c r="G61" t="n">
+      <c r="K61" t="n">
         <v>0.8631</v>
       </c>
     </row>
@@ -2205,21 +3305,39 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>相互最近傍フラグ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>前向き・後向きの双方向で互いに第1候補であるか (1/0)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>(fwd_rank == 1 and bwd_rank == 1)</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
         <v>0.5037</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="J62" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G62" t="n">
+      <c r="K62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2234,21 +3352,39 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>前向き距離順位</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>接続元ノードから見た接続先ノードの距離順位 (1が最寄り)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>rank of tgt from src</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
         <v>0.5037</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="I63" t="n">
+        <v>-0.0856</v>
+      </c>
+      <c r="J63" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G63" t="n">
+      <c r="K63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2263,21 +3399,39 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>ILP採択フラグ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>大域的整数線形計画法(ILP)によって最終採用されたか (1/0)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>edge in ILP solution</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>0.5036</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="J64" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G64" t="n">
+      <c r="K64" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2292,21 +3446,39 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Y軸変位 (μm)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>接続元から接続先へのY方向の符号付き物理移動量</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>(y_tgt - y_src) * s_y</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
         <v>0.5032</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>POS_LOW</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="I65" t="n">
+        <v>-0.0201</v>
+      </c>
+      <c r="J65" t="n">
         <v>0.005</v>
       </c>
-      <c r="G65" t="n">
+      <c r="K65" t="n">
         <v>-1.62</v>
       </c>
     </row>
@@ -2321,21 +3493,39 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>3D-UNet検出確率</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>ノード (Node)</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3D-UNetが細胞中心であると判定した信頼度スコア</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Sigmoid(logits)</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>0.5</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>0.0045</v>
       </c>
-      <c r="G66" t="n">
+      <c r="K66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2350,21 +3540,39 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>時間間隔 (フレーム数)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>接続元フレームと接続先フレームの時間差 (通常1)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>t_tgt - t_src</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
         <v>0.5</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>0.0041</v>
       </c>
-      <c r="G67" t="n">
+      <c r="K67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2379,21 +3587,39 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>後向き距離順位</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>接続先ノードから見た接続元ノードの逆向き距離順位</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>rank of src to tgt</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
         <v>0.5</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
         <v>0.0041</v>
       </c>
-      <c r="G68" t="n">
+      <c r="K68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2408,21 +3634,39 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>後向き競合距離マージン (μm)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>エッジ (Edge)</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>逆向き探索における第1候補と第2候補の距離差</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>dist_bwd_cand2 - dist_bwd_cand1</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
         <v>0.5</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>POS_HIGH</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>POS_HIGH</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
         <v>0.0041</v>
       </c>
-      <c r="G69" t="n">
+      <c r="K69" t="n">
         <v>999</v>
       </c>
     </row>
